--- a/artfynd/A 23581-2024 artfynd.xlsx
+++ b/artfynd/A 23581-2024 artfynd.xlsx
@@ -1160,7 +1160,7 @@
         <v>118553503</v>
       </c>
       <c r="B6" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>118553573</v>
       </c>
       <c r="B7" t="n">
-        <v>97750</v>
+        <v>97757</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
